--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67B0C2-EC34-4D96-AAAB-828CF8997396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A19E-9642-4CC2-BB7D-B73082D1E9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="930" windowWidth="27990" windowHeight="14415" activeTab="2" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="810" yWindow="1065" windowWidth="27990" windowHeight="14415" activeTab="3" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
-    <sheet name="1214event" sheetId="2" r:id="rId1"/>
-    <sheet name="1207event" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="1207event" sheetId="3" r:id="rId1"/>
+    <sheet name="1214event" sheetId="2" r:id="rId2"/>
+    <sheet name="1221event" sheetId="4" r:id="rId3"/>
+    <sheet name="resporn" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -282,6 +283,178 @@
   </si>
   <si>
     <t>底知れぬ不安だけが、ひっそりと黒く渦巻いていた。</t>
+  </si>
+  <si>
+    <t>12月21日。</t>
+  </si>
+  <si>
+    <t>この地獄のような崩壊都市に足を踏み入れてから、ちょうど3週間が経っていた。</t>
+  </si>
+  <si>
+    <t>雪が舞い散る廃墟の中、紫苑はふらつく足取りで歩みを進めていた。</t>
+  </si>
+  <si>
+    <t>ボロボロになった制服は泥と煤で汚れきっている。</t>
+  </si>
+  <si>
+    <t>ここに来た日のことなど、もうずっと昔のように思えた。</t>
+  </si>
+  <si>
+    <t>ただ生き延びるためだけに、化け物たちから逃げ、泥水をすすり、息を潜めるだけの日々。</t>
+  </si>
+  <si>
+    <t>いつからだろう。この肌を刺すような冬の風を浴びても、</t>
+  </si>
+  <si>
+    <t>寒さを一切感じなくなってしまったのは。自分の身体が徐々に「人間」から遠ざかっていくような、</t>
+  </si>
+  <si>
+    <t>そんな薄ら寒い恐怖だけがずっと付き纏っていた。</t>
+  </si>
+  <si>
+    <t>それでも、希望は捨てていなかった。</t>
+  </si>
+  <si>
+    <t>先週、瓦礫の隙間から見上げた夜空に、一筋の流星を見たのだ。</t>
+  </si>
+  <si>
+    <t>「生きて帰れますように」——こんな狂った世界で、柄にもなく星に願い事なんてしてしまった自分を、少しだけ可笑しく思ったっけ。</t>
+  </si>
+  <si>
+    <t>その願いが、ようやく届いたのだろうか。</t>
+  </si>
+  <si>
+    <t>「あ……」</t>
+  </si>
+  <si>
+    <t>灰色に霞む視界のずっと先に、たくさんの人影が見えた。</t>
+  </si>
+  <si>
+    <t>異形の化け物じゃない。統制の取れた、人間の姿だ。</t>
+  </si>
+  <si>
+    <t>助かった。やっと、やっとこの終わらない地獄から抜け出せる……！</t>
+  </si>
+  <si>
+    <t>こわばっていた紫苑の顔に、安堵の涙が浮かぶ。彼女は瓦礫につまずきながらも夢中で駆け寄り、千切れんばかりに大きく空へ手を振った。</t>
+  </si>
+  <si>
+    <t>「ここです！ 私は、ここに——」</t>
+  </si>
+  <si>
+    <t>声に呼応するように、人影たちがこちらを向いたように見えた。</t>
+  </si>
+  <si>
+    <t>次の瞬間。</t>
+  </si>
+  <si>
+    <t>彼らの元から、無数の熱くきらめく光が瞬いた。</t>
+  </si>
+  <si>
+    <t>——ドッ、ガァァンッ！！</t>
+  </si>
+  <si>
+    <t>「え……？」</t>
+  </si>
+  <si>
+    <t>鼓膜を破るような轟音と共に、視界がオレンジ色の閃光と真っ黒な飛沫に染まった。</t>
+  </si>
+  <si>
+    <t>強烈な爆発の衝撃が、紫苑の細い身体を容赦なく吹き飛ばし、貫く。</t>
+  </si>
+  <si>
+    <t>熱い。</t>
+  </si>
+  <si>
+    <t>ひどく、熱い。痛い。</t>
+  </si>
+  <si>
+    <t>雪の冷たさすらとうに感じなくなっていたはずの身体が、内側から焼けるような激痛に悲鳴を上げている。</t>
+  </si>
+  <si>
+    <t>四肢を食い破る、圧倒的な暴力。</t>
+  </si>
+  <si>
+    <t>わけがわからなかった。彼らは人間で、助けに来てくれたはずじゃなかったのか。</t>
+  </si>
+  <si>
+    <t>薄れゆく意識と、焼け焦げるような痛みの中で、紫苑の口から血の混じった掠れ声が零れ落ちた。</t>
+  </si>
+  <si>
+    <t>「何故────</t>
+  </si>
+  <si>
+    <t>BGM：C:\Users\user\.antigravity\game\files\BGM\001_OP001.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM:"C:\Users\user\.antigravity\game\files\BGM\bad.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\event\1221a.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\event\1221b.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\event\1221c.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どれだけの時間が流れたのか、知る術はない。</t>
+  </si>
+  <si>
+    <t>自分がどこにいるのか、自身の肉体がどうなってしまったのかもわからない。</t>
+  </si>
+  <si>
+    <t>視覚も聴覚も奪われたそこは、ただ暗く、深い水の底に沈んでいるかのような空間だった。</t>
+  </si>
+  <si>
+    <t>波が起こるたび、様々なものが引き寄せられるように集まってくる。</t>
+  </si>
+  <si>
+    <t>その波を何度感じたことだろうか。</t>
+  </si>
+  <si>
+    <t>数えきれないほどの長い時間、ただ何かを待ち続けていたような気がした。</t>
+  </si>
+  <si>
+    <t>——ある瞬間。</t>
+  </si>
+  <si>
+    <t>爆発でも起きたかのような凄まじい衝撃と共に、無数の記憶が、溢れんばかりの『レリクス』が流れ込んでくるのを感じた。</t>
+  </si>
+  <si>
+    <t>眩しいほどの光。</t>
+  </si>
+  <si>
+    <t>燃えるような熱。</t>
+  </si>
+  <si>
+    <t>全身に鉛を詰め込まれたかのような、這い蹲りたくなるほどの質量と重力。</t>
+  </si>
+  <si>
+    <t>あらゆる感覚が暴力的に蘇り、無理やり現実へと引きずり出されたその瞬間。</t>
+  </si>
+  <si>
+    <t>紫苑は、見覚えのある景色の中に立っていた。</t>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\event\resp.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG&lt;:C:\Users\user\.antigravity\game\files\BGM\resporn.mp3</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -644,6 +817,122 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24EFD97-1CBD-4B2F-99EB-66112E329FCB}">
+  <dimension ref="A1:A32"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -911,122 +1200,6 @@
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24EFD97-1CBD-4B2F-99EB-66112E329FCB}">
-  <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1037,9 +1210,286 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308FE447-E3D0-4326-A67A-812DC7B972B5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39E5C1-2FD3-4BA9-9C7E-7ED67CF62693}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A19E-9642-4CC2-BB7D-B73082D1E9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CB21D-94B9-402F-B7C0-7B3D8E0CA94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="1065" windowWidth="27990" windowHeight="14415" activeTab="3" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="1350" yWindow="1065" windowWidth="27990" windowHeight="14415" activeTab="5" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
     <sheet name="1214event" sheetId="2" r:id="rId2"/>
     <sheet name="1221event" sheetId="4" r:id="rId3"/>
     <sheet name="resporn" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="1221wildhunt" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="160">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -454,6 +456,348 @@
   </si>
   <si>
     <t>BG&lt;:C:\Users\user\.antigravity\game\files\BGM\resporn.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>午前の始まり</t>
+    <rPh sb="0" eb="2">
+      <t>ゴゼン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>午後の始まり</t>
+    <rPh sb="0" eb="2">
+      <t>ゴゴ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜の始まり</t>
+    <rPh sb="0" eb="1">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上の敵のレベルが1上がり、敵の数量が50増え、ウェーブ数が1増えます。敵の大きさが1.2倍になります。夜の探索時のように、探索コマンドでも敵が発生します。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>スウリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="56" eb="59">
+      <t>タンサクジ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地名付きのヘクスにいない場合、何を選んでも突破線が始まります。目標距離は12010、敵レベルは周囲のヘクスで一番高いレベル、発生数は200，発生間隔は0.5秒で開始されます。</t>
+    <rPh sb="0" eb="2">
+      <t>チメイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>トッパセン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="62" eb="65">
+      <t>ハッセイスウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1221イベントで主人公は死に、リスポーンイベントが始まります。</t>
+    <rPh sb="9" eb="12">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>撤退を選択しようとすると、撤退のできない戦闘です　と言われます。全滅するとリスポーンイベントが始まります。</t>
+    <rPh sb="0" eb="2">
+      <t>テッタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テッタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゼンメツ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月21日、夜。</t>
+  </si>
+  <si>
+    <t>それは「ワイルドハント」と呼ばれる、この世の終わりそのものだった。</t>
+  </si>
+  <si>
+    <t>数千、数万――いや、もはや数えることすら無意味なほどの化け物の群れが、雪に沈む廃墟を黒く染め上げていく。</t>
+  </si>
+  <si>
+    <t>それは文字通りの百鬼夜行だった。</t>
+  </si>
+  <si>
+    <t>強固なビルすらも、果てしなく続く異形の蹂躙の前では枯れ木のようにへし折られ、轟音と共に粉々に砕け散っていく。地響きが足元から這い上がり、空気を震わせる咆哮が絶え間なく耳を打つ。</t>
+  </si>
+  <si>
+    <t>私たちが息を潜めていたささやかな隠れ家など、その圧倒的な暴力の前では何の役にも立たなかった。</t>
+  </si>
+  <si>
+    <t>迫り来る壁の崩壊と地鳴りに追われ、私たちは雪が吹きすさぶ地上へと放り出された。</t>
+  </si>
+  <si>
+    <t>前後左右、見渡す限りの黒い波。</t>
+  </si>
+  <si>
+    <t>逃げ場など、最初からどこにも用意されていなかったのだ。</t>
+  </si>
+  <si>
+    <t>生き残るための選択肢は、狂気じみたひとつだけ。</t>
+  </si>
+  <si>
+    <t>この常軌を逸した群れのど真ん中へと突っ込み、弾薬と命を削りながら「中心突破」を図ること。</t>
+  </si>
+  <si>
+    <t>ただそれだけだった。</t>
+  </si>
+  <si>
+    <t>凍りついた指で引き金に触れながら、目の前の地獄を睨みつける。</t>
+  </si>
+  <si>
+    <t>けれど、心の奥底で黒く濁った絶望が、冷たい雪のように降り積もっていくのを止められなかった。</t>
+  </si>
+  <si>
+    <t>仮に。</t>
+  </si>
+  <si>
+    <t>仮に、この何万という群れの中を奇跡的に抜け出せたとして。</t>
+  </si>
+  <si>
+    <t>この、すべてが壊れ、誰もいなくなった世界の果てで――。</t>
+  </si>
+  <si>
+    <t>突破して、一体どこに行けばいいというのだろう？</t>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\event\wildhunt.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM:C:\Users\user\.antigravity\game\files\BGM\wildhunt.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>このまま掛け合いが始まる。</t>
+    </r>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>人目</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>ニンメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント反応</t>
+    <rPh sb="7" eb="9">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>人目</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>ニンメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント終了。このあと移動しようが探索しようが休息しようが指定の通りの突破戦が始まる。</t>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キュウソク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トッパ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ハジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -461,7 +805,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,6 +820,19 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -500,9 +857,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1493,4 +1859,204 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21991C8-0D24-4F9B-ABDB-2C65B69633C9}">
+  <dimension ref="A2:D9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>46377</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>46377</v>
+      </c>
+      <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>46377</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>46378</v>
+      </c>
+      <c r="B9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12DEB48-0936-4471-BA70-091E6191D4B7}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CB21D-94B9-402F-B7C0-7B3D8E0CA94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41537528-521E-4B38-B6F4-21CE2896AA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="1065" windowWidth="27990" windowHeight="14415" activeTab="5" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="615" yWindow="780" windowWidth="27990" windowHeight="14415" activeTab="5" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -751,6 +751,37 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>イベント終了。このあと移動しようが探索しようが休息しようが指定の通りの突破戦が始まる。</t>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キュウソク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トッパ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <r>
       <t>2</t>
     </r>
@@ -764,39 +795,39 @@
       </rPr>
       <t>人目</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いる場合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <rPh sb="1" eb="3">
       <t>ニンメ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベント終了。このあと移動しようが探索しようが休息しようが指定の通りの突破戦が始まる。</t>
-    <rPh sb="4" eb="6">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>タンサク</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>キュウソク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>トオ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>トッパ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>セン</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ハジ</t>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -805,7 +836,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,6 +862,13 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
@@ -1185,109 +1223,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24EFD97-1CBD-4B2F-99EB-66112E329FCB}">
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1301,269 +1339,269 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -1577,194 +1615,194 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308FE447-E3D0-4326-A67A-812DC7B972B5}">
   <dimension ref="A1:A53"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>106</v>
       </c>
@@ -1778,79 +1816,79 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39E5C1-2FD3-4BA9-9C7E-7ED67CF62693}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -1864,12 +1902,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21991C8-0D24-4F9B-ABDB-2C65B69633C9}">
   <dimension ref="A2:D9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>46377</v>
       </c>
@@ -1880,7 +1918,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>46377</v>
       </c>
@@ -1891,7 +1929,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>46377</v>
       </c>
@@ -1902,12 +1940,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4">
       <c r="D7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>46378</v>
       </c>
@@ -1927,114 +1965,114 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12DEB48-0936-4471-BA70-091E6191D4B7}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1">
       <c r="A16" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>155</v>
       </c>
@@ -2042,17 +2080,17 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41537528-521E-4B38-B6F4-21CE2896AA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4B5445-F1BD-43F7-83D3-37DB57D8BFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="780" windowWidth="27990" windowHeight="14415" activeTab="5" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="1890" yWindow="495" windowWidth="26205" windowHeight="14850" firstSheet="1" activeTab="7" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="resporn" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
     <sheet name="1221wildhunt" sheetId="7" r:id="rId6"/>
+    <sheet name="ikebukuro01" sheetId="8" r:id="rId7"/>
+    <sheet name="ikebukuro02" sheetId="10" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="213">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -829,6 +832,188 @@
     <rPh sb="6" eb="8">
       <t>バアイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(静かに歌い上げる)</t>
+  </si>
+  <si>
+    <t>静かな夜明け 光が落ちて</t>
+  </si>
+  <si>
+    <t>孤独な風が 頬を撫でる</t>
+  </si>
+  <si>
+    <t>過ぎ去った日々 静寂の中で</t>
+  </si>
+  <si>
+    <t>ただ一人 目を閉じる</t>
+  </si>
+  <si>
+    <t>[Chorus]</t>
+  </si>
+  <si>
+    <t>うたかたに　消える記憶(メモリー)</t>
+  </si>
+  <si>
+    <t>絶望が根を張る</t>
+  </si>
+  <si>
+    <t>狂い咲く 五十二の世界</t>
+  </si>
+  <si>
+    <t>千切れゆく 正気（こころ）を繋ぐ祈り</t>
+  </si>
+  <si>
+    <t>懐かしい日々を取り戻すまで</t>
+  </si>
+  <si>
+    <t>ここは偽りの天国</t>
+  </si>
+  <si>
+    <t>終わらない 彷徨（さまよ）いの果て</t>
+  </si>
+  <si>
+    <t>いのちが燃えつきるまで</t>
+  </si>
+  <si>
+    <t>終わらない　巡礼(じゅんれい)の旅</t>
+  </si>
+  <si>
+    <t>[Quiet]</t>
+  </si>
+  <si>
+    <t>(ささやくように)</t>
+  </si>
+  <si>
+    <t>(いのる)</t>
+  </si>
+  <si>
+    <t>マギア ピルグリム...</t>
+  </si>
+  <si>
+    <t>[END]</t>
+  </si>
+  <si>
+    <t>BGM:"C:\Users\user\.antigravity\game\files\BGM\unknoun_terror.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像："C:\Users\user\.antigravity\game\files\event\ikebukuro01.jpg"</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冷たいコンクリートと、固く閉ざされたシャッター。</t>
+  </si>
+  <si>
+    <t>内部へ続く侵入口を探し、壁伝いに歩を進めていたその時だった。</t>
+  </si>
+  <si>
+    <t>――不意に、世界の音が消えた。</t>
+  </si>
+  <si>
+    <t>直後、臓腑を直接氷の刃で撫でられたかのような、すさまじい悪寒が全身を貫く。</t>
+  </si>
+  <si>
+    <t>物理的な冷気ではない。見えない巨大な手に心臓をわしづかみにされ、無理やり脈動を止められたような、生物としての根源的な恐怖。</t>
+  </si>
+  <si>
+    <t>息ができない。足が床に縫い付けられたように動かない。</t>
+  </si>
+  <si>
+    <t>濁った視界の先。閉ざされたシャッターの前に、一瞬、濃密な闇が凝びりついた。</t>
+  </si>
+  <si>
+    <t>姿を見た気がしたのは、ほんの一瞬。</t>
+  </si>
+  <si>
+    <t>網膜に焼き付いた残像が溶けるより早く、鼓膜を通さず、脳の髄を直接震わせる「声」が響いた。</t>
+  </si>
+  <si>
+    <t>『 ――今はまだ、ここにくる時ではない 』</t>
+  </si>
+  <si>
+    <t>次の瞬間、心臓を握り潰すような圧迫感は嘘のように消え去っていた。</t>
+  </si>
+  <si>
+    <t>荒い呼吸を繰り返す目の前には、ただ無機質なシャッターだけが、拒絶するようにそびえ立っている。</t>
+  </si>
+  <si>
+    <t>光を一切反射しない漆黒の虚無が、ただ静かにこちらを見下ろしている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強固なシェルターを探し、廃墟の壁を這うように歩き回るが、見つかる扉という扉はすべて完全に沈黙し、生存者を拒絶するように固く閉ざされていた。</t>
+  </si>
+  <si>
+    <t>このままでは、夜の群れに呑まれる。</t>
+  </si>
+  <si>
+    <t>絶望が脳裏をよぎった、その時だった。</t>
+  </si>
+  <si>
+    <t>――不意に、周囲の空気が凍りついた。</t>
+  </si>
+  <si>
+    <t>物理的な温度低下ではない。見えない巨大な手に心臓を直接わしづかみにされ、生暖かい臓腑に氷の杭を打ち込まれたような、圧倒的な悪寒。</t>
+  </si>
+  <si>
+    <t>息が詰まり、視界がノイズでひび割れる。</t>
+  </si>
+  <si>
+    <t>その歪みの中に、一瞬だけ「それ」が立っていた。</t>
+  </si>
+  <si>
+    <t>姿を見た気がしたのは、ほんの瞬きほどの時間。</t>
+  </si>
+  <si>
+    <t>交感神経が警鐘を鳴らすより早く、頭蓋の奥深く、脳髄を直接撫でるように「声」が響いた。</t>
+  </si>
+  <si>
+    <t>『 ――こちらへ、来い 』</t>
+  </si>
+  <si>
+    <t>恐怖で硬直するはずの足が、見えない糸に引かれるように前へと進む。抗えない引力。</t>
+  </si>
+  <si>
+    <t>導かれるままに角を曲がると、そこには幻覚で見た光景と同じ、暴力的な力で破壊されたシャッターの残骸が、暗い臓腑の口を開けていた。</t>
+  </si>
+  <si>
+    <t>踏み込もうとした瞬間。</t>
+  </si>
+  <si>
+    <t>漆黒の闇の奥へ、あの少女のような影が、ふい、と空間に溶け込むように消えていくのを見た……ような気がした。</t>
+  </si>
+  <si>
+    <t>それが救済の道か、あるいはさらに深い地獄への誘いなのかは分からない。</t>
+  </si>
+  <si>
+    <t>だが、立ち止まれば死の群れに追いつかれる。ただ確かなのは、進む以外の選択肢はとうに失われているということだけだった。</t>
+  </si>
+  <si>
+    <t>焦燥が足筋を焼いている。地上を埋め尽くさん勢いのワイルドハントの襲撃。</t>
+    <rPh sb="12" eb="14">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イキオ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シュウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分厚い鋼鉄を紙屑のように引き裂いた開口部。その前に佇む、光を一切反射しない漆黒のシルエット。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2097,4 +2282,318 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1B31EE-A44B-4D9B-AE6F-77340BD3A785}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEA09D1-A31D-4EBF-99EA-367C43E4D131}">
+  <dimension ref="A1:A30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C393974-77C1-42AA-91D4-CDF928338E82}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4B5445-F1BD-43F7-83D3-37DB57D8BFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB9BB71-5485-4115-996C-2838ED9E457A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="495" windowWidth="26205" windowHeight="14850" firstSheet="1" activeTab="7" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="0" yWindow="630" windowWidth="26205" windowHeight="14850" firstSheet="1" activeTab="2" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
     <sheet name="1214event" sheetId="2" r:id="rId2"/>
-    <sheet name="1221event" sheetId="4" r:id="rId3"/>
-    <sheet name="resporn" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
-    <sheet name="1221wildhunt" sheetId="7" r:id="rId6"/>
-    <sheet name="ikebukuro01" sheetId="8" r:id="rId7"/>
-    <sheet name="ikebukuro02" sheetId="10" r:id="rId8"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
+    <sheet name="1217event" sheetId="11" r:id="rId3"/>
+    <sheet name="1221event" sheetId="4" r:id="rId4"/>
+    <sheet name="resporn" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="1221wildhunt" sheetId="7" r:id="rId7"/>
+    <sheet name="ikebukuro01" sheetId="8" r:id="rId8"/>
+    <sheet name="ikebukuro02" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="247">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1014,6 +1015,117 @@
   </si>
   <si>
     <t>分厚い鋼鉄を紙屑のように引き裂いた開口部。その前に佇む、光を一切反射しない漆黒のシルエット。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景：C:\Users\user\.antigravity\game\files\event\1217a.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM："C:\Users\user\.antigravity\game\files\BGM\unknoun_terror.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どんよりと濁った午後の空を、紫苑はただぼんやりと見上げていた。</t>
+  </si>
+  <si>
+    <t>崩壊した都市の上空で、不吉な黒い鳥の群れが弧を描いている。</t>
+  </si>
+  <si>
+    <t>あの瓦礫の向こうには、化け物に襲われた誰かの死体でもあるのだろうか。</t>
+  </si>
+  <si>
+    <t>「次は、私かもしれないな……」</t>
+  </si>
+  <si>
+    <t>乾いた風に自嘲をこぼした直後、紫苑は息を呑んだ。</t>
+  </si>
+  <si>
+    <t>旋回するカラスたちの真下、うず高く積まれた瓦礫の山の頂に、</t>
+  </si>
+  <si>
+    <t>ふわりと佇む人影が見えたのだ。</t>
+  </si>
+  <si>
+    <t>逆光と砂埃に霞み、表情までは分からない。</t>
+  </si>
+  <si>
+    <t>だが、風に揺れる髪の輪郭が、紫苑の脳髄に強烈な既視感を引きずり出す。</t>
+  </si>
+  <si>
+    <t>あれは、記憶の最奥に焼き付いた「あの姿」だ。</t>
+  </si>
+  <si>
+    <t>泥水をすすり、息を潜め、ただ明日を迎えることだけを考える日々。</t>
+  </si>
+  <si>
+    <t>狂気に満ちた生存競争は、いつしか彼女の中から、最も重要な記憶すらも削り落としていた。</t>
+  </si>
+  <si>
+    <t>――だが、思い出した。</t>
+  </si>
+  <si>
+    <t>私がこの地獄を這いずり回っている理由は、ただ無様に生き延びるためなんかじゃない。</t>
+  </si>
+  <si>
+    <t>名前も顔も思い出せない、あの「誰か」を、必ず探し出すことだったのだと。</t>
+  </si>
+  <si>
+    <t>紫苑の足は憑かれたように前へと踏み出していた。</t>
+  </si>
+  <si>
+    <t>「……待って！」</t>
+  </si>
+  <si>
+    <t>肺が焼け焦げるように痛む。瓦礫に足をとられ、</t>
+  </si>
+  <si>
+    <t>剥き出しの鉄筋に肌を裂かれて何度も無様に転びながら、</t>
+  </si>
+  <si>
+    <t>紫苑は無我夢中で頂上へと駆け登った。</t>
+  </si>
+  <si>
+    <t>だが、這々の体でたどり着いたそこには、</t>
+  </si>
+  <si>
+    <t>無情な風と遠ざかる羽音だけが残されていた。足跡すら、どこにもない。</t>
+  </si>
+  <si>
+    <t>「待って……誰なんだよ、あれはッ……！」</t>
+  </si>
+  <si>
+    <t>幻覚だったのか。思い出そうとするたび脳髄に分厚いノイズが走り、</t>
+  </si>
+  <si>
+    <t>一番大切なはずの『顔』と『名前』が砂のようにこぼれ落ちていく。</t>
+  </si>
+  <si>
+    <t>どうしてこんなにも胸が引き裂かれそうになるのか。</t>
+  </si>
+  <si>
+    <t>紫苑は血の滲む手で足元の瓦礫を掴むと、</t>
+  </si>
+  <si>
+    <t>傍らのコンクリート壁へ狂ったように何度も何度も殴りつけた。</t>
+  </si>
+  <si>
+    <t>ガンッ、ガンッと暴力的な音が響き、やがて手の中の石が砕け散る。</t>
+  </si>
+  <si>
+    <t>同時にその場へ力なく崩れ落ちた彼女の喉からは、</t>
+  </si>
+  <si>
+    <t>行き場のない悲痛な嗚咽だけが漏れ、ただ空しく廃墟の空へと吸い込まれていった。</t>
+  </si>
+  <si>
+    <t>背景：C:\Users\user\.antigravity\game\files\event\1217b.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1521,6 +1633,123 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C393974-77C1-42AA-91D4-CDF928338E82}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
@@ -1798,6 +2027,187 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBC8581-4FA5-4294-B723-43CE6A099BFD}">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308FE447-E3D0-4326-A67A-812DC7B972B5}">
   <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1998,7 +2408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39E5C1-2FD3-4BA9-9C7E-7ED67CF62693}">
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2084,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21991C8-0D24-4F9B-ABDB-2C65B69633C9}">
   <dimension ref="A2:D9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2147,7 +2557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12DEB48-0936-4471-BA70-091E6191D4B7}">
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2284,7 +2694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1B31EE-A44B-4D9B-AE6F-77340BD3A785}">
   <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2370,7 +2780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEA09D1-A31D-4EBF-99EA-367C43E4D131}">
   <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -2479,121 +2889,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C393974-77C1-42AA-91D4-CDF928338E82}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB9BB71-5485-4115-996C-2838ED9E457A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EF909A-8918-44A2-A852-15E6F0E8D8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="630" windowWidth="26205" windowHeight="14850" firstSheet="1" activeTab="2" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="0" yWindow="630" windowWidth="26205" windowHeight="14850" firstSheet="2" activeTab="9" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="1221wildhunt" sheetId="7" r:id="rId7"/>
     <sheet name="ikebukuro01" sheetId="8" r:id="rId8"/>
     <sheet name="ikebukuro02" sheetId="10" r:id="rId9"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId10"/>
+    <sheet name="tow_res" sheetId="12" r:id="rId10"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="257">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1127,6 +1128,40 @@
       <t>ハイケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像："C:\Users\user\.antigravity\game\files\event\tow_spo01.jpg"</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『――もう少し前まで、もどってみる？』</t>
+  </si>
+  <si>
+    <t>この感覚を知っている。</t>
+  </si>
+  <si>
+    <t>永遠とも思える空白の底。</t>
+  </si>
+  <si>
+    <t>肉体を失い、視覚も聴覚もないはずの意識が、</t>
+  </si>
+  <si>
+    <t>確かに「誰か」を捉えていた。</t>
+  </si>
+  <si>
+    <t>響く声。浮かび上がる姿。</t>
+  </si>
+  <si>
+    <t>記憶すら剥がれ落ち、</t>
+  </si>
+  <si>
+    <t>自我も曖昧な今の君に、</t>
+  </si>
+  <si>
+    <t>その言葉の意味を理解する術はないのだが。</t>
   </si>
 </sst>
 </file>
@@ -1634,6 +1669,72 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C5C13E-C137-465E-9294-1A6EBF97ACDF}">
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C393974-77C1-42AA-91D4-CDF928338E82}">
   <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EF909A-8918-44A2-A852-15E6F0E8D8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1234DE9A-39E1-4665-B9B1-DE31190785CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="630" windowWidth="26205" windowHeight="14850" firstSheet="2" activeTab="9" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="765" yWindow="525" windowWidth="26205" windowHeight="14850" firstSheet="4" activeTab="12" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,9 @@
     <sheet name="ikebukuro01" sheetId="8" r:id="rId8"/>
     <sheet name="ikebukuro02" sheetId="10" r:id="rId9"/>
     <sheet name="tow_res" sheetId="12" r:id="rId10"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId11"/>
+    <sheet name="2R1201ev" sheetId="13" r:id="rId11"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId12"/>
+    <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="331">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1162,6 +1164,504 @@
   </si>
   <si>
     <t>その言葉の意味を理解する術はないのだが。</t>
+  </si>
+  <si>
+    <t>BGM:マップのまま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景：東京ヘクスの背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……」</t>
+  </si>
+  <si>
+    <t>「……」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……！？」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>抗いようのない絶望に呑み込まれ、私の命は確実にすり潰された。</t>
+  </si>
+  <si>
+    <t>だが、気づけば紫苑は、見覚えのある「始まりの景色」の中に立っていた。</t>
+  </si>
+  <si>
+    <t>何百年、あるいは何千年。</t>
+  </si>
+  <si>
+    <t>光のない泥の底を這いずり、自我を削られ、途方もない時間をかけてこの場所まで遡ってきたような気がする。</t>
+  </si>
+  <si>
+    <t>しかし、その間の記憶は一切ない。</t>
+  </si>
+  <si>
+    <t>ただ、無限にも等しい年月を彷徨い続けたという「魂の摩耗」だけが、鉛のように全身へとのしかかっていた。</t>
+  </si>
+  <si>
+    <t>震える両手を見つめる。傷ひとつない、まっさらな肉体。</t>
+  </si>
+  <si>
+    <t>まるで、あの絶望の夜など最初から存在しなかったかのように、世界は静まり返っている。</t>
+  </si>
+  <si>
+    <t>…巡礼の旅は始まったばかりだ</t>
+  </si>
+  <si>
+    <t>紫苑が右側に出てくる</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>息絶える瞬間の、内臓が凍りつくような恐怖と無慈悲な暗闇だけが、網膜にひどく鮮明にこびりついている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>――死んでから目覚めるまで、一体どれほどの時間が過ぎたのだろうか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑が右側に出てくる、</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>淡々とした声だった。威圧するでもなく、ただ事実を述べるような口調。</t>
+  </si>
+  <si>
+    <t>「悪魔……」</t>
+  </si>
+  <si>
+    <t>「そう身構えるな。今のお前に、危害を加えるつもりはない」</t>
+  </si>
+  <si>
+    <t>紫苑は答えず、目の前の異形をまじまじと観察した。</t>
+  </si>
+  <si>
+    <t>「素直だな」</t>
+  </si>
+  <si>
+    <t>紫苑は黙り込んだ。魔の力を借りて、戦う力を得る——その構図に、何かが引っかかる。</t>
+  </si>
+  <si>
+    <t>「なぜ、私に構うの」</t>
+  </si>
+  <si>
+    <t>その問いに、プロセルはわずかに口角を上げた。</t>
+  </si>
+  <si>
+    <t>紫苑は、すぐには言葉を返せなかった。</t>
+  </si>
+  <si>
+    <t>「その度に、時間ごと引き戻される。……厄介なことに、同じ場所で何度も足止めを食っている」</t>
+  </si>
+  <si>
+    <t>紫苑の背筋に、冷たいものが走った。</t>
+  </si>
+  <si>
+    <t>もっと聞きたいことがあった。だが、プロセルの声が、不意にわずかに揺れた。</t>
+  </si>
+  <si>
+    <t>「……む」</t>
+  </si>
+  <si>
+    <t>「どうしたの」</t>
+  </si>
+  <si>
+    <t>「……この対話体、そう長くは保たんようだな」</t>
+  </si>
+  <si>
+    <t>「え……」</t>
+  </si>
+  <si>
+    <t>視界が、端から白く滲み始める。</t>
+  </si>
+  <si>
+    <t>「待って、まだ——」</t>
+  </si>
+  <si>
+    <t>プロセルの声が、遠のいていく。</t>
+  </si>
+  <si>
+    <t>目が覚めた瞬間、頭の芯にべったりと張り付くような不快感があった。</t>
+  </si>
+  <si>
+    <t>夢だったはずなのに、忘れられない。何ひとつ欠けることなく、記憶に残っている。</t>
+  </si>
+  <si>
+    <t>げんなりとした気分のまま体を起こそうとして、右手の違和感に気づいた。</t>
+  </si>
+  <si>
+    <t>握られていた。</t>
+  </si>
+  <si>
+    <t>紫苑はゆっくりと手を開く。</t>
+  </si>
+  <si>
+    <t>小さな木の板切れだった。使い古された質感。拙いような、それでいて妙に達筆な文字で、二文字。</t>
+  </si>
+  <si>
+    <t>「道場」</t>
+  </si>
+  <si>
+    <t>紫苑は、しばらくその板を無言で見つめた。</t>
+  </si>
+  <si>
+    <t>——これは、いったい何なのか。</t>
+  </si>
+  <si>
+    <t>紫苑は長旅の疲れからうっかり眠ってしまったようだった。</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナガタビ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ネム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しかし景色はさっきいた場所と同じように見える、静かだ…。</t>
+    <rPh sb="3" eb="5">
+      <t>ケシキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>シズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……ここは夢、だよね」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……足りないのは、間違いないと思う」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「欲しいけど、例えば…代わりに何を取られるの」</t>
+    <rPh sb="1" eb="2">
+      <t>ホ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「私の本体は今、閉じ込められている。……この姿も、かろうじて作った分け身のようなものでな」</t>
+    <rPh sb="3" eb="5">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>スガタ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「余と契約して…魔法少女になってくれ…いや、なれ！」</t>
+    <rPh sb="1" eb="2">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えの出ない問いだけが、穏やかな昼の明かりの静けさの中に残された。</t>
+    <rPh sb="12" eb="13">
+      <t>オダ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（プロセルが不透明度50%で左から出てくる。）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うなだれていた首をもたげると、視界の中央に、それはいた。白い長髪、黒い角、背の翼。明らかに人ではない姿。</t>
+    <rPh sb="7" eb="8">
+      <t>クビ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>身の危険を感じたが、何故か警戒心は薄れた。目が二つ、鼻と口がひとつずつ。輪郭も定かでない化け物ばかり見てきた身には、それだけで十分"話が通じる相手"に見えた。</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キケン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナゼ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「はじめまして、紫苑。　私はプロセル。ヒトの呼ぶところの、悪魔だ」</t>
+    <rPh sb="8" eb="10">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「単刀直入に言おう。……今のお前たちには、目的に対して力が足りない。」</t>
+    <rPh sb="12" eb="13">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「力が欲しいか。」</t>
+    <rPh sb="1" eb="2">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「私が求めているのは、お前たちの集めているヒトの魂の欠片…俗に言うSPだ」</t>
+    <rPh sb="24" eb="25">
+      <t>タマシイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カケラ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ゾク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「それを少しだけ私に託せ。それを使って貴様らの力を増してやろう。……悪くない話だろう」</t>
+    <rPh sb="4" eb="5">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「そこから出るには、ちょっとばかり力が必要でな。それに、お前が役立ちそうなのだよ」</t>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……あなたも、助けが欲しい…と？」</t>
+    <rPh sb="8" eb="9">
+      <t>タス</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「そう聞こえるなら、そうなのだろうな。……だが、悪い話ではないはずだ。私はお前に力を、お前は私に手段を…ウィンウィン、というやつだろう」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「余もこの世界の異常を、あちこちで調べている。……何度も、災いの渦に呑まれてな」</t>
+    <rPh sb="1" eb="2">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ここは…いや、ここや外の場所は、どうなっているの？」</t>
+    <rPh sb="11" eb="12">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「災いの渦……?」</t>
+    <rPh sb="1" eb="2">
+      <t>ワザワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「そして、その災いの渦の中心に——どうやら、お前が近いと踏んでいる」</t>
+    <rPh sb="7" eb="8">
+      <t>ワザワ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「私が、原因ってこと?」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「原因とは言っていない。……ただ、お前の動き、お前の縁に繋がってようにも見える、というだけの話だ」</t>
+    <rPh sb="18" eb="19">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツナ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「これは私自身ではない。分身の、そのまた写しだ。……荷が重かったか」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ちっ…災いが…仕方がない、これだけは持っておけ、仮契約だ」</t>
+    <rPh sb="4" eb="5">
+      <t>ワザワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シカタ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケイヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景：現在滞在中のヘクスの背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>タイザイチュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1735,6 +2235,93 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989486F6-E3F9-4DC7-B073-5C24037F3D46}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C393974-77C1-42AA-91D4-CDF928338E82}">
   <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1848,6 +2435,308 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A97B92-7523-4891-A880-CB63AAA25BDE}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1234DE9A-39E1-4665-B9B1-DE31190785CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F14163-1E5F-4E01-BB6E-5DEDBFC26972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="525" windowWidth="26205" windowHeight="14850" firstSheet="4" activeTab="12" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="2R1201ev" sheetId="13" r:id="rId11"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId12"/>
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
+    <sheet name="DOJO" sheetId="16" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="344">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1437,10 +1438,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>（プロセルが不透明度50%で左から出てくる。）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>うなだれていた首をもたげると、視界の中央に、それはいた。白い長髪、黒い角、背の翼。明らかに人ではない姿。</t>
     <rPh sb="7" eb="8">
       <t>クビ</t>
@@ -1660,6 +1657,242 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（プロセル"C:\Users\user\.antigravity\game\files\CHR\010001b.png"が不透明度50%で左から出てくる。）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM:"C:\Users\user\.antigravity\game\files\BGM\002_menu.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\MAP\dojo.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>眼を開けるとそこは何かの道場のようで、中央に道着を着たプロセルが立っていた</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ドウギ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よく来たな、ここは貴様らを鍛え直すDOJOだ</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ど、道場…？</t>
+    <rPh sb="2" eb="4">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NO！　DOJO！　貴様らはここで心・技・体を鍛え上げ最強の魔法少女となるのだ</t>
+    <rPh sb="10" eb="12">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カラダ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サイキョウ</t>
+    </rPh>
+    <rPh sb="30" eb="34">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ド、DOJO…？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>All Right！ DOJO！　貴様らが溜め込んだSPをより効率よく使用し、貴様らを作り変え…鍛え上げるのだ</t>
+    <rPh sb="17" eb="19">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちょっと待て作り変えって何だ</t>
+    <rPh sb="4" eb="5">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセルの残した、道場と書いた札を見つめていると紫苑は突如めまいに襲われ、視界は暗闇に包まれた。</t>
+    <rPh sb="5" eb="6">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トツジョ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シカイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>クラヤミ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分け身の分け身である余にはそれを説明する分の知識を与えられていない、早く強くなって余の本体を解放してくれ。</t>
+    <rPh sb="0" eb="1">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カイホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2448,7 +2681,7 @@
         <v>257</v>
       </c>
       <c r="C1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G1" t="s">
         <v>274</v>
@@ -2466,17 +2699,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2486,7 +2719,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2511,12 +2744,12 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2536,12 +2769,12 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -2566,17 +2799,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -2586,17 +2819,17 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -2611,7 +2844,7 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2621,12 +2854,12 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -2656,7 +2889,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -2671,7 +2904,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -2732,6 +2965,107 @@
     <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894D19D9-00DC-4DED-8255-C52D5A226D4C}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F14163-1E5F-4E01-BB6E-5DEDBFC26972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8651142-82C7-4F56-B4A7-2BB636C18AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8651142-82C7-4F56-B4A7-2BB636C18AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9D892-94F6-4946-9C78-3459259E8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="3075" yWindow="360" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="Sheet3" sheetId="9" r:id="rId12"/>
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
+    <sheet name="JIKU" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="363">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1893,6 +1894,295 @@
     </rPh>
     <rPh sb="46" eb="48">
       <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景：C:\Users\user\.antigravity\game\files\MAP\m(k,11)r.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑が右に出てくる</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側から不透明度50%のプロセル"C:\Users\user\.antigravity\game\files\CHR\010001b.png"が出てくる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>フトウメイド</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「これはヒトが造った時空を超える装置だ」</t>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「うわっ！……はあ…はあ…」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「貴様がここを訪れたことで余が造っていた平行時空との接続が完了した。」</t>
+    <rPh sb="5" eb="7">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オトズ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヘイコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……？」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「招待しよう、何はともあれ時空の館へ」</t>
+    <rPh sb="5" eb="7">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヤカタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗転</t>
+    <rPh sb="0" eb="2">
+      <t>アンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一枚絵(背景ではなくイベントグラフィック)　C:\Users\user\.antigravity\game\files\MAP\jiku-.jpg</t>
+    <rPh sb="0" eb="3">
+      <t>イチマイエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「ここは現在世界の時空をゆがめている輩のスキをついて余が造った避難所、訓練施設」</t>
+    <rPh sb="8" eb="10">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヤカラ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ヒナンジョ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラの立ち絵は表示しない。</t>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「地上とここでは貴様らの成長度合いは共有されない。レリクスと宝石が頼りだ。」</t>
+    <rPh sb="5" eb="7">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドア</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ホウセキ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「用意された幻影を倒すことで道場で訓練に使うSPといくらかのレリクスが見つけられるはずだ」</t>
+    <rPh sb="5" eb="7">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンエイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「……」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「例によって話せる時間は少ない…あとは使って覚えろ。」</t>
+    <rPh sb="5" eb="6">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「…地上来て楽しんでんなコイツ…」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道場解放後に地上、シルバードームに到達するとイベントが始まる。</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウタツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ハジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3074,6 +3364,122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF88277-A34F-4C4C-8EFC-0E2C09FF6627}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9D892-94F6-4946-9C78-3459259E8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9AD9A1-4F95-4685-82F2-B08F41F209FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="360" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="675" yWindow="315" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
     <sheet name="JIKU" sheetId="17" r:id="rId15"/>
+    <sheet name="Sheet2" sheetId="18" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="377">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -2183,6 +2184,209 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天隕晶</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アキラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>七星宝剣</t>
+    <rPh sb="0" eb="1">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱点属性の敵への攻撃のダメージを2倍にする。</t>
+    <rPh sb="0" eb="2">
+      <t>ジャクテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+5 CH率+5 CH倍率+5</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在精神力の1/10を攻撃力に加算する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理攻撃には適用されない。</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理攻撃にのみ適用される。</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精神力+5 リロード+5 CH率+5</t>
+    <rPh sb="0" eb="3">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在生命力の1/10を攻撃力に加算する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生命力+5 回避+5 CH倍率+5</t>
+    <rPh sb="0" eb="3">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妙見鑑</t>
+    <rPh sb="0" eb="2">
+      <t>ミョウケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェイスエリアの奥深くにあるスターストーンを見てからスカイツリーに行くと手に入る。</t>
+    <rPh sb="8" eb="10">
+      <t>オクフカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スケルトンエリアを下った先にあるキャリバーンを見てから上野にいくと手に入る。</t>
+    <rPh sb="9" eb="10">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ウエノ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地下21階にある。</t>
+    <rPh sb="0" eb="2">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3480,6 +3684,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27536E43-80CF-4D3F-9264-77E06E30D30F}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>

--- a/public/files/event/event.xlsx
+++ b/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9AD9A1-4F95-4685-82F2-B08F41F209FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A4CCDE-42AC-4980-96CB-C01EE53B91B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="315" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="1320" yWindow="420" windowWidth="26205" windowHeight="14850" firstSheet="8" activeTab="16" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -29,6 +29,8 @@
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
     <sheet name="JIKU" sheetId="17" r:id="rId15"/>
     <sheet name="Sheet2" sheetId="18" r:id="rId16"/>
+    <sheet name="塔21F" sheetId="19" r:id="rId17"/>
+    <sheet name="塔21Fb" sheetId="20" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="408">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -2388,6 +2390,166 @@
     <rPh sb="4" eb="5">
       <t>カイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ曲が演奏中でなければ　bgm："C:\Users\user\.antigravity\game\files\BGM\tow_Frozen Silence.mp3"</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>エンソウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント一枚絵："C:\Users\user\.antigravity\game\files\event\tow_21.jpg"</t>
+    <rPh sb="4" eb="7">
+      <t>イチマイエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凍てつくような冷気が肺を刺す。巨大な神殿のような広間へ足を踏み入れた紫苑は、その異様な光景に思わず足を止めた。</t>
+  </si>
+  <si>
+    <t>その時、鼓膜ではなく紫苑の脳内に直接、あの傲慢で冷ややかな声が響き渡った。</t>
+  </si>
+  <si>
+    <t>『――よくたどり着いた、人の子よ』</t>
+  </si>
+  <si>
+    <t>紫苑が手にした武器を強く握り直し、腰を落として身構えたその瞬間――氷像の周囲の大気が急激に圧縮され、けたたましい音鳴りと共に防衛機構が作動した。</t>
+  </si>
+  <si>
+    <t>視界を白く染め上げるほどの猛吹雪と、不可視の氷の刃が、侵入者をミンチにせんと全方位から殺意を持って吹き荒れる。</t>
+  </si>
+  <si>
+    <t>殺戮の嵐が吹き荒れる中、プロセルの声だけは他人事のようにひどく呑気だった。</t>
+  </si>
+  <si>
+    <t>紫苑は口元を歪めて悪態をつくと、凍てつく床を強く蹴り飛ばした。吹き荒れる死の吹雪を掻き分け、その中心にある巨大な氷の塊を粉砕するための死闘が幕を開ける。</t>
+  </si>
+  <si>
+    <t>紫苑「うおっ……でっか……」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広間の中央には、荘厳で巨大な悪魔の氷像が鎮座していた。分厚い氷に閉ざされたその姿は、透き通るような神々しさと、背筋が凍るほどの魔性を同時に放ち、絶対的な静寂の中で眠りについている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……本当に、いいんだな？」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「言ってくれる……ッ！」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル『それが余の力を封じている原因だ。さあ、その忌まわしい氷像を砕け！』</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル『反撃をかわして、うまく壊せ』</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>声の主は日ごろ世話になっている道場主、いや時空館のメイド…もとい悪魔プロセルだった。</t>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セワ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ドウジョウヌシ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヤカタ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm："C:\Users\user\.antigravity\game\files\BGM\005_JOIN_US.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一枚絵："C:\Users\user\.antigravity\game\files\event\tow_21b.jpg"</t>
+    <rPh sb="0" eb="3">
+      <t>イチマイエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の瞬間、巨大な氷像は無数の破片となって吹き飛び、ダイヤモンドダストのようにきらきらと宙を舞う。</t>
+  </si>
+  <si>
+    <t>その眩い光の粉の只中から、プロセルが優雅に舞い降りた。</t>
+  </si>
+  <si>
+    <t>「素晴らしい。よくぞ砕いてみせたな、我が麗しの主よ」</t>
+  </si>
+  <si>
+    <t>疲労で重くなった顔を上げ、紫苑が短く告げると、プロセルは不満げに目を細めた。</t>
+  </si>
+  <si>
+    <t>ふわりと冷たい香りを漂わせて紫苑の耳元へと近づき、甘く囁く。</t>
+  </si>
+  <si>
+    <t>「早まるな。この不可解な塔の正体も、余が封じられていた理由も、まだ何一つ判明してはおらぬ。当然、契約は継続だ。……それに、凍てつくような絶望の中で足掻く貴様には、ひどく興味を惹かれるのでな」</t>
+  </si>
+  <si>
+    <t>悪魔の冷たい指先が、紫苑の頬をそっと撫でた。</t>
+  </si>
+  <si>
+    <t>呆れるほど尊大で、底知れない力を持った悪魔からの猛アピール。</t>
+  </si>
+  <si>
+    <t>最後の一撃が深々と突き刺さり、氷像全体を震わせる。鼓膜を劈くような甲高い亀裂音が神殿に響き渡った。</t>
+    <rPh sb="3" eb="5">
+      <t>イチゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>フル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>透き通るような氷を纏った悪魔は、息を切らして膝をつく紫苑を見下ろし、酷薄な唇に艶やかな笑みを浮かべる。</t>
+    <rPh sb="12" eb="14">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……これで、終わりか。それじゃあ、あなたとの契約もここまでかな」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アルカナの導き次第では、余が直接その盤面に降り立ち、助力を与えてやってもよいぞ。せいぜい楽しみに待っていることだ。……何なら、今からでも手伝ってやろうか？」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑は冷たい空気を肺に吸い込み、やれやれと小さく息をついた。どうやら、この悪魔とは、まだ長い付き合いになりそうだ。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3765,6 +3927,183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64A577B-5BB8-4CF4-8A0F-C0F786591683}">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B38310-6FC5-4CEC-90C4-F48C7825049A}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>407</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
